--- a/src/Excelsior.Tests/NullableTests.WithRender.verified.xlsx
+++ b/src/Excelsior.Tests/NullableTests.WithRender.verified.xlsx
@@ -227,7 +227,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Number"/>
     <column index="2" property="String"/>

--- a/src/Excelsior.Tests/NullableTests.WithRender.verified.xlsx
+++ b/src/Excelsior.Tests/NullableTests.WithRender.verified.xlsx
@@ -44,15 +44,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -173,56 +164,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F4"/>
-  <conditionalFormatting sqref="A2:A4">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(A2))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B4">
-    <cfRule type="containsBlanks" dxfId="0" priority="2">
-      <formula>LEN(TRIM(B2))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C4">
-    <cfRule type="containsBlanks" dxfId="0" priority="3">
-      <formula>LEN(TRIM(C2))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
-    <cfRule type="containsBlanks" dxfId="0" priority="4">
-      <formula>LEN(TRIM(D2))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
-    <cfRule type="containsBlanks" dxfId="0" priority="5">
-      <formula>LEN(TRIM(E2))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
-    <cfRule type="containsBlanks" dxfId="0" priority="6">
-      <formula>LEN(TRIM(F2))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="6">
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="A2:A4">
-      <formula1>LEN(TRIM(A2))&gt;0</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="B2:B4">
-      <formula1>LEN(TRIM(B2))&gt;0</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="C2:C4">
-      <formula1>LEN(TRIM(C2))&gt;0</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="D2:D4">
-      <formula1>LEN(TRIM(D2))&gt;0</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="E2:E4">
-      <formula1>LEN(TRIM(E2))&gt;0</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="F2:F4">
-      <formula1>LEN(TRIM(F2))&gt;0</formula1>
-    </dataValidation>
-  </dataValidations>
 </worksheet>
 </file>
 
